--- a/OJT_Task_List.xlsx
+++ b/OJT_Task_List.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cguarin\Desktop\ProjectOJT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DCAA3D21-0DCF-40DA-82B8-7FA81166B07E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11760BFE-9CB0-4388-965C-387868AECFDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E13C8D52-9F8B-4FDB-9F13-2929AF0C8F2B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>No.</t>
   </si>
@@ -54,6 +54,9 @@
   </si>
   <si>
     <t>Learning Github</t>
+  </si>
+  <si>
+    <t>Learning Gitbash Command</t>
   </si>
 </sst>
 </file>
@@ -426,7 +429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9904E6F-5F07-4A56-A088-B8CA076BEF91}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -458,6 +461,17 @@
         <v>46080</v>
       </c>
     </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1">
+        <v>46081</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/OJT_Task_List.xlsx
+++ b/OJT_Task_List.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cguarin\Desktop\ProjectOJT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mel2\Desktop\OJT\ProjectOJT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11760BFE-9CB0-4388-965C-387868AECFDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8837F2B3-1F8B-4FAE-AF01-D3D2383AE07F}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E13C8D52-9F8B-4FDB-9F13-2929AF0C8F2B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{E13C8D52-9F8B-4FDB-9F13-2929AF0C8F2B}"/>
   </bookViews>
   <sheets>
     <sheet name="Edmel" sheetId="1" r:id="rId1"/>
@@ -23,23 +23,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>No.</t>
   </si>
@@ -57,13 +46,22 @@
   </si>
   <si>
     <t>Learning Gitbash Command</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>T</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -429,14 +427,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9904E6F-5F07-4A56-A088-B8CA076BEF91}">
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -450,7 +448,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -461,7 +459,7 @@
         <v>46080</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -470,6 +468,39 @@
       </c>
       <c r="C3" s="1">
         <v>46081</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="1">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="1">
+        <v>46084</v>
       </c>
     </row>
   </sheetData>
@@ -480,7 +511,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34896598-9D1A-42D6-AA9E-3E540AFF8B1A}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -489,7 +520,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B35264AA-0E55-4822-9DDD-A3E6378A411F}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -498,7 +529,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27DEEDAD-1EF5-4EE5-BA1D-B2D48AB08D32}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/OJT_Task_List.xlsx
+++ b/OJT_Task_List.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cguarin\Desktop\ProjectOJT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikeeee\Desktop\OJT Tasks\ProjectOJT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11760BFE-9CB0-4388-965C-387868AECFDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E87BF8F0-BDE4-421D-B069-E17F870DD519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E13C8D52-9F8B-4FDB-9F13-2929AF0C8F2B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{E13C8D52-9F8B-4FDB-9F13-2929AF0C8F2B}"/>
   </bookViews>
   <sheets>
     <sheet name="Edmel" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
   <si>
     <t>No.</t>
   </si>
@@ -57,16 +57,42 @@
   </si>
   <si>
     <t>Learning Gitbash Command</t>
+  </si>
+  <si>
+    <t>Learning Git Bash</t>
+  </si>
+  <si>
+    <t>02/27/2026</t>
+  </si>
+  <si>
+    <t>Changing IP of Switch</t>
+  </si>
+  <si>
+    <t>Printer Maintenance (Head/Power Cleaning)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -92,9 +118,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -430,13 +462,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9904E6F-5F07-4A56-A088-B8CA076BEF91}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -450,7 +482,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -461,7 +493,7 @@
         <v>46080</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -479,26 +511,82 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34896598-9D1A-42D6-AA9E-3E540AFF8B1A}">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.109375" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" customWidth="1"/>
+    <col min="3" max="3" width="16.77734375" customWidth="1"/>
+    <col min="4" max="4" width="17" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B35264AA-0E55-4822-9DDD-A3E6378A411F}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B35264AA-0E55-4822-9DDD-A3E6378A411F}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27DEEDAD-1EF5-4EE5-BA1D-B2D48AB08D32}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/OJT_Task_List.xlsx
+++ b/OJT_Task_List.xlsx
@@ -1,28 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cguarin\Desktop\ProjectOJT\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11760BFE-9CB0-4388-965C-387868AECFDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E13C8D52-9F8B-4FDB-9F13-2929AF0C8F2B}"/>
+    <workbookView windowWidth="28800" windowHeight="12885" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Edmel" sheetId="1" r:id="rId1"/>
     <sheet name="Mike" sheetId="2" r:id="rId2"/>
-    <sheet name="Czi-jei" sheetId="3" r:id="rId3"/>
+    <sheet name="Czi-Jei" sheetId="3" r:id="rId3"/>
     <sheet name="Sir Chan" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -39,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="9">
   <si>
     <t>No.</t>
   </si>
@@ -58,29 +49,401 @@
   <si>
     <t>Learning Gitbash Command</t>
   </si>
+  <si>
+    <t>Performance Tasks</t>
+  </si>
+  <si>
+    <t>Learn Github</t>
+  </si>
+  <si>
+    <t>27Feb26</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -88,25 +451,496 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="58" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -155,7 +989,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -188,26 +1022,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -240,23 +1057,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -418,25 +1218,20 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9904E6F-5F07-4A56-A088-B8CA076BEF91}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.09166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -450,56 +1245,456 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="23">
         <v>46080</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="23">
         <v>46081</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34896598-9D1A-42D6-AA9E-3E540AFF8B1A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B35264AA-0E55-4822-9DDD-A3E6378A411F}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="C3:H43"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="1.625" style="1" customWidth="1"/>
+    <col min="2" max="6" width="9" style="1"/>
+    <col min="7" max="7" width="13.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" s="1" customFormat="1" spans="3:8">
+      <c r="C3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="3:8">
+      <c r="C4" s="5"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="7"/>
+    </row>
+    <row r="5" spans="3:8">
+      <c r="C5" s="5"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="7"/>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="3:8">
+      <c r="C6" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="3:8">
+      <c r="C7" s="12">
+        <v>1</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="14"/>
+      <c r="F7" s="15"/>
+      <c r="G7" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="17"/>
+    </row>
+    <row r="8" spans="3:8">
+      <c r="C8" s="12"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="15"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+    </row>
+    <row r="9" spans="3:8">
+      <c r="C9" s="12"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="15"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+    </row>
+    <row r="10" spans="3:8">
+      <c r="C10" s="12"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+    </row>
+    <row r="11" spans="3:8">
+      <c r="C11" s="12"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+    </row>
+    <row r="12" spans="3:8">
+      <c r="C12" s="12"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+    </row>
+    <row r="13" spans="3:8">
+      <c r="C13" s="12"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+    </row>
+    <row r="14" spans="3:8">
+      <c r="C14" s="12"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
+    </row>
+    <row r="15" spans="3:8">
+      <c r="C15" s="12"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+    </row>
+    <row r="16" spans="3:8">
+      <c r="C16" s="12"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+    </row>
+    <row r="17" spans="3:8">
+      <c r="C17" s="12"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+    </row>
+    <row r="18" spans="3:8">
+      <c r="C18" s="12"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+    </row>
+    <row r="19" spans="3:8">
+      <c r="C19" s="12"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+    </row>
+    <row r="20" spans="3:8">
+      <c r="C20" s="12"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+    </row>
+    <row r="21" spans="3:8">
+      <c r="C21" s="12"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+    </row>
+    <row r="22" spans="3:8">
+      <c r="C22" s="12"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+    </row>
+    <row r="23" spans="3:8">
+      <c r="C23" s="12"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+    </row>
+    <row r="24" spans="3:8">
+      <c r="C24" s="12"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+    </row>
+    <row r="25" spans="3:8">
+      <c r="C25" s="12"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+    </row>
+    <row r="26" spans="3:8">
+      <c r="C26" s="12"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+    </row>
+    <row r="27" spans="3:8">
+      <c r="C27" s="12"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+    </row>
+    <row r="28" spans="3:8">
+      <c r="C28" s="12"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+    </row>
+    <row r="29" spans="3:8">
+      <c r="C29" s="12"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+    </row>
+    <row r="30" spans="3:8">
+      <c r="C30" s="12"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
+    </row>
+    <row r="31" spans="3:8">
+      <c r="C31" s="12"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="17"/>
+    </row>
+    <row r="32" spans="3:8">
+      <c r="C32" s="12"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+    </row>
+    <row r="33" spans="3:8">
+      <c r="C33" s="12"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+    </row>
+    <row r="34" spans="3:8">
+      <c r="C34" s="12"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+    </row>
+    <row r="35" spans="3:8">
+      <c r="C35" s="12"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="17"/>
+    </row>
+    <row r="36" spans="3:8">
+      <c r="C36" s="12"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17"/>
+    </row>
+    <row r="37" spans="3:8">
+      <c r="C37" s="12"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+    </row>
+    <row r="38" spans="3:8">
+      <c r="C38" s="12"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="17"/>
+      <c r="H38" s="17"/>
+    </row>
+    <row r="39" spans="3:8">
+      <c r="C39" s="12"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="15"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
+    </row>
+    <row r="40" spans="3:8">
+      <c r="C40" s="12"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+    </row>
+    <row r="41" spans="3:8">
+      <c r="C41" s="12"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="17"/>
+      <c r="H41" s="17"/>
+    </row>
+    <row r="42" spans="3:8">
+      <c r="C42" s="12"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="17"/>
+    </row>
+    <row r="43" spans="3:8">
+      <c r="C43" s="18"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="21"/>
+      <c r="G43" s="22"/>
+      <c r="H43" s="22"/>
+    </row>
+  </sheetData>
+  <mergeCells count="39">
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="D12:F12"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="C3:H5"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27DEEDAD-1EF5-4EE5-BA1D-B2D48AB08D32}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>